--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_12.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0339592907611992</v>
+        <v>0.02985473679034637</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008468882373272653</v>
+        <v>0.008460309764744066</v>
       </c>
       <c r="C2" t="n">
-        <v>76356972</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>76356972</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>50891196</v>
+        <v>3923513</v>
       </c>
       <c r="L2" t="n">
-        <v>25419066</v>
+        <v>1637060</v>
       </c>
       <c r="M2" t="n">
-        <v>5610114</v>
+        <v>286476</v>
       </c>
       <c r="N2" t="n">
-        <v>236402</v>
+        <v>5968</v>
       </c>
       <c r="O2" t="n">
-        <v>3273686</v>
+        <v>155018</v>
       </c>
       <c r="P2" t="n">
-        <v>1233279</v>
+        <v>876</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999871253967285</v>
+        <v>0.9999843835830688</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8003993630409241</v>
+        <v>0.7066823244094849</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6492222547531128</v>
+        <v>0.5137864947319031</v>
       </c>
       <c r="T2" t="n">
-        <v>0.561474084854126</v>
+        <v>0.3753852546215057</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1601911932229996</v>
+        <v>0.03761739656329155</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6173994541168213</v>
+        <v>0.3807289898395538</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7487123608589172</v>
+        <v>0.3850549459457397</v>
       </c>
       <c r="X2" t="n">
-        <v>76356972</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>76356972</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>57941310</v>
+        <v>4760658</v>
       </c>
       <c r="AG2" t="n">
-        <v>36227525</v>
+        <v>3049090</v>
       </c>
       <c r="AH2" t="n">
-        <v>9662257</v>
+        <v>809872</v>
       </c>
       <c r="AI2" t="n">
-        <v>711841</v>
+        <v>59470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5526744</v>
+        <v>462174</v>
       </c>
       <c r="AK2" t="n">
-        <v>2163347</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556514024734497</v>
+        <v>0.9542856216430664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117959141731262</v>
+        <v>0.9129269123077393</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578110933303833</v>
+        <v>0.857567310333252</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6610904335975647</v>
+        <v>0.6599931120872498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9018860459327698</v>
+        <v>0.9016656875610352</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314352869987488</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.009097034286255497</v>
+        <v>0.007844881538992333</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002028431794565072</v>
+        <v>0.002026924819488894</v>
       </c>
       <c r="C3" t="n">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>50891196</v>
+        <v>3923513</v>
       </c>
       <c r="E3" t="n">
-        <v>9208703</v>
+        <v>991621</v>
       </c>
       <c r="F3" t="n">
-        <v>346591</v>
+        <v>47698</v>
       </c>
       <c r="G3" t="n">
-        <v>41540</v>
+        <v>5307</v>
       </c>
       <c r="H3" t="n">
-        <v>26373</v>
+        <v>4412</v>
       </c>
       <c r="I3" t="n">
-        <v>1891</v>
+        <v>70</v>
       </c>
       <c r="J3" t="n">
-        <v>121152447</v>
+        <v>10069521</v>
       </c>
       <c r="K3" t="n">
-        <v>124302941</v>
+        <v>9814861</v>
       </c>
       <c r="L3" t="n">
-        <v>143952677</v>
+        <v>11513342</v>
       </c>
       <c r="M3" t="n">
-        <v>181849767</v>
+        <v>14993199</v>
       </c>
       <c r="N3" t="n">
-        <v>195193135</v>
+        <v>16173082</v>
       </c>
       <c r="O3" t="n">
-        <v>189348803</v>
+        <v>15650735</v>
       </c>
       <c r="P3" t="n">
-        <v>194772945</v>
+        <v>16220551</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8409488201141357</v>
+        <v>0.7890210747718811</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6382901668548584</v>
+        <v>0.4881714582443237</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4973951578140259</v>
+        <v>0.3027887344360352</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2193135321140289</v>
+        <v>0.06613768637180328</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5337905287742615</v>
+        <v>0.3021074831485748</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5307772755622864</v>
+        <v>0.004514300264418125</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57941310</v>
+        <v>4760658</v>
       </c>
       <c r="Z3" t="n">
-        <v>2388917</v>
+        <v>196517</v>
       </c>
       <c r="AA3" t="n">
-        <v>102998</v>
+        <v>8569</v>
       </c>
       <c r="AB3" t="n">
-        <v>82445</v>
+        <v>6849</v>
       </c>
       <c r="AC3" t="n">
-        <v>370</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>121153428</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>134305137</v>
+        <v>11215310</v>
       </c>
       <c r="AG3" t="n">
-        <v>154182186</v>
+        <v>12771731</v>
       </c>
       <c r="AH3" t="n">
-        <v>184629817</v>
+        <v>15335364</v>
       </c>
       <c r="AI3" t="n">
-        <v>196067555</v>
+        <v>16295127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>190776255</v>
+        <v>15852474</v>
       </c>
       <c r="AK3" t="n">
-        <v>195027618</v>
+        <v>16208628</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9574480652809143</v>
+        <v>0.9573714733123779</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9096980094909668</v>
+        <v>0.9092389345169067</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8566599488258362</v>
+        <v>0.8559883832931519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6603851318359375</v>
+        <v>0.6590496301651001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9011626243591309</v>
+        <v>0.9007097482681274</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9310588836669922</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07359085111687913</v>
+        <v>0.06595131411877257</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0320094986107273</v>
+        <v>0.03198862993387096</v>
       </c>
       <c r="C4" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>11571846</v>
+        <v>1439052</v>
       </c>
       <c r="E4" t="n">
-        <v>25419066</v>
+        <v>1637060</v>
       </c>
       <c r="F4" t="n">
-        <v>2323371</v>
+        <v>217307</v>
       </c>
       <c r="G4" t="n">
-        <v>199689</v>
+        <v>25292</v>
       </c>
       <c r="H4" t="n">
-        <v>280930</v>
+        <v>34433</v>
       </c>
       <c r="I4" t="n">
-        <v>28687</v>
+        <v>279</v>
       </c>
       <c r="J4" t="n">
-        <v>981</v>
+        <v>99</v>
       </c>
       <c r="K4" t="n">
-        <v>12691059</v>
+        <v>1628505</v>
       </c>
       <c r="L4" t="n">
-        <v>13734039</v>
+        <v>1549205</v>
       </c>
       <c r="M4" t="n">
-        <v>4381645</v>
+        <v>476676</v>
       </c>
       <c r="N4" t="n">
-        <v>1239347</v>
+        <v>152682</v>
       </c>
       <c r="O4" t="n">
-        <v>2028693</v>
+        <v>252143</v>
       </c>
       <c r="P4" t="n">
-        <v>413921</v>
+        <v>1399</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999935626983643</v>
+        <v>0.9999921917915344</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8201732635498047</v>
+        <v>0.7455853223800659</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6437097787857056</v>
+        <v>0.5006515979766846</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5274957418441772</v>
+        <v>0.3352013528347015</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1851470619440079</v>
+        <v>0.04795769974589348</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5725587606430054</v>
+        <v>0.3368920087814331</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6211844086647034</v>
+        <v>0.008923977613449097</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2511522</v>
+        <v>213160</v>
       </c>
       <c r="Z4" t="n">
-        <v>36227525</v>
+        <v>3049090</v>
       </c>
       <c r="AA4" t="n">
-        <v>1002730</v>
+        <v>84162</v>
       </c>
       <c r="AB4" t="n">
-        <v>67105</v>
+        <v>5695</v>
       </c>
       <c r="AC4" t="n">
-        <v>13976</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>826</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2688863</v>
+        <v>228056</v>
       </c>
       <c r="AG4" t="n">
-        <v>3504530</v>
+        <v>290816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1601595</v>
+        <v>134511</v>
       </c>
       <c r="AI4" t="n">
-        <v>364927</v>
+        <v>30637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>601241</v>
+        <v>50404</v>
       </c>
       <c r="AK4" t="n">
-        <v>159248</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565488696098328</v>
+        <v>0.9558260440826416</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107457995414734</v>
+        <v>0.9110792279243469</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8572351336479187</v>
+        <v>0.8567771315574646</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6607376337051392</v>
+        <v>0.6595210433006287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9015241861343384</v>
+        <v>0.9011874794960022</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312470555305481</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>809007</v>
+        <v>139499</v>
       </c>
       <c r="E5" t="n">
-        <v>3548008</v>
+        <v>403040</v>
       </c>
       <c r="F5" t="n">
-        <v>5610114</v>
+        <v>286476</v>
       </c>
       <c r="G5" t="n">
-        <v>376992</v>
+        <v>39956</v>
       </c>
       <c r="H5" t="n">
-        <v>841417</v>
+        <v>76863</v>
       </c>
       <c r="I5" t="n">
-        <v>93359</v>
+        <v>280</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9625204</v>
+        <v>1049121</v>
       </c>
       <c r="L5" t="n">
-        <v>14404618</v>
+        <v>1716393</v>
       </c>
       <c r="M5" t="n">
-        <v>5668874</v>
+        <v>659649</v>
       </c>
       <c r="N5" t="n">
-        <v>841516</v>
+        <v>84268</v>
       </c>
       <c r="O5" t="n">
-        <v>2859218</v>
+        <v>358104</v>
       </c>
       <c r="P5" t="n">
-        <v>1090255</v>
+        <v>193174</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999950528144836</v>
+        <v>0.9999939799308777</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8870121836662292</v>
+        <v>0.8368892669677734</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8575332760810852</v>
+        <v>0.8010722398757935</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9491139650344849</v>
+        <v>0.9307793974876404</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9894645214080811</v>
+        <v>0.9855659008026123</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9752523899078369</v>
+        <v>0.9628260731697083</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9923843145370483</v>
+        <v>0.9881473779678345</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>97782</v>
+        <v>8204</v>
       </c>
       <c r="Z5" t="n">
-        <v>1040083</v>
+        <v>87997</v>
       </c>
       <c r="AA5" t="n">
-        <v>9662257</v>
+        <v>809872</v>
       </c>
       <c r="AB5" t="n">
-        <v>120231</v>
+        <v>10066</v>
       </c>
       <c r="AC5" t="n">
-        <v>351023</v>
+        <v>29345</v>
       </c>
       <c r="AD5" t="n">
-        <v>7612</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2575090</v>
+        <v>211976</v>
       </c>
       <c r="AG5" t="n">
-        <v>3596159</v>
+        <v>304363</v>
       </c>
       <c r="AH5" t="n">
-        <v>1616731</v>
+        <v>136253</v>
       </c>
       <c r="AI5" t="n">
-        <v>366077</v>
+        <v>30766</v>
       </c>
       <c r="AJ5" t="n">
-        <v>606160</v>
+        <v>50948</v>
       </c>
       <c r="AK5" t="n">
-        <v>160187</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733484983444214</v>
+        <v>0.97319495677948</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9640490412712097</v>
+        <v>0.9637439846992493</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837055206298828</v>
+        <v>0.9835060834884644</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962989091873169</v>
+        <v>0.9962595701217651</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938868880271912</v>
+        <v>0.9938260316848755</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983826875686646</v>
+        <v>0.9983697533607483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>199779</v>
+        <v>24138</v>
       </c>
       <c r="E6" t="n">
-        <v>257492</v>
+        <v>28224</v>
       </c>
       <c r="F6" t="n">
-        <v>261925</v>
+        <v>23946</v>
       </c>
       <c r="G6" t="n">
-        <v>236402</v>
+        <v>5968</v>
       </c>
       <c r="H6" t="n">
-        <v>108941</v>
+        <v>7823</v>
       </c>
       <c r="I6" t="n">
-        <v>13223</v>
+        <v>122</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78965</v>
+        <v>6656</v>
       </c>
       <c r="Z6" t="n">
-        <v>64825</v>
+        <v>5410</v>
       </c>
       <c r="AA6" t="n">
-        <v>132325</v>
+        <v>11168</v>
       </c>
       <c r="AB6" t="n">
-        <v>711841</v>
+        <v>59470</v>
       </c>
       <c r="AC6" t="n">
-        <v>84179</v>
+        <v>7046</v>
       </c>
       <c r="AD6" t="n">
-        <v>5783</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>242</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>101688</v>
+        <v>23396</v>
       </c>
       <c r="E7" t="n">
-        <v>647385</v>
+        <v>111619</v>
       </c>
       <c r="F7" t="n">
-        <v>1301928</v>
+        <v>158441</v>
       </c>
       <c r="G7" t="n">
-        <v>531214</v>
+        <v>63982</v>
       </c>
       <c r="H7" t="n">
-        <v>3273686</v>
+        <v>155018</v>
       </c>
       <c r="I7" t="n">
-        <v>276761</v>
+        <v>648</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>256</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9731</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>359557</v>
+        <v>30278</v>
       </c>
       <c r="AB7" t="n">
-        <v>91949</v>
+        <v>7760</v>
       </c>
       <c r="AC7" t="n">
-        <v>5526744</v>
+        <v>462174</v>
       </c>
       <c r="AD7" t="n">
-        <v>144667</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>291</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>8739</v>
+        <v>2420</v>
       </c>
       <c r="E8" t="n">
-        <v>72451</v>
+        <v>14701</v>
       </c>
       <c r="F8" t="n">
-        <v>147830</v>
+        <v>29284</v>
       </c>
       <c r="G8" t="n">
-        <v>89912</v>
+        <v>18145</v>
       </c>
       <c r="H8" t="n">
-        <v>771032</v>
+        <v>128612</v>
       </c>
       <c r="I8" t="n">
-        <v>1233279</v>
+        <v>876</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>338</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>974</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3985</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3197</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151693</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2163347</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
